--- a/data/trans_dic/P19C09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,8</t>
+          <t>1,77; 4,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,42</t>
+          <t>0,87; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,23</t>
+          <t>1,91; 5,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,04</t>
+          <t>2,73; 6,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,32</t>
+          <t>0,97; 3,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,63</t>
+          <t>1,19; 3,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,88</t>
+          <t>2,59; 5,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,78</t>
+          <t>1,13; 2,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,96</t>
+          <t>1,78; 3,91</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,83</t>
+          <t>1,51; 3,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,4</t>
+          <t>0,75; 2,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,02</t>
+          <t>1,71; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,89</t>
+          <t>2,19; 4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,3</t>
+          <t>1,96; 4,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,7</t>
+          <t>2,04; 4,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,81</t>
+          <t>2,04; 3,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,15</t>
+          <t>1,58; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,82</t>
+          <t>2,25; 3,85</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,47</t>
+          <t>1,39; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,81</t>
+          <t>1,62; 4,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,14</t>
+          <t>1,63; 4,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,19</t>
+          <t>1,43; 4,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,47</t>
+          <t>0,52; 2,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,67</t>
+          <t>1,73; 3,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,03</t>
+          <t>1,27; 2,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,01</t>
+          <t>1,3; 2,95</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,09</t>
+          <t>1,6; 4,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,33; 3,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,19</t>
+          <t>1,78; 4,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,15</t>
+          <t>1,67; 3,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,89</t>
+          <t>2,31; 5,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,96</t>
+          <t>2,34; 5,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,5</t>
+          <t>1,91; 3,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,9</t>
+          <t>2,2; 4,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,06</t>
+          <t>2,32; 4,04</t>
         </is>
       </c>
     </row>
@@ -1123,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,22; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,64</t>
+          <t>2,31; 3,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,9</t>
+          <t>2,51; 3,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,48</t>
+          <t>2,17; 3,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,34</t>
+          <t>2,09; 3,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,43</t>
+          <t>2,45; 3,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,76</t>
+          <t>1,88; 2,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,2</t>
+          <t>2,35; 3,24</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7794; 22939</t>
+          <t>8457; 23191</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4997; 20231</t>
+          <t>5148; 20060</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10406; 27438</t>
+          <t>10046; 27293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14243; 32510</t>
+          <t>14692; 33877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5928; 20791</t>
+          <t>6082; 20642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5762; 19768</t>
+          <t>6478; 20892</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25579; 49620</t>
+          <t>26330; 51025</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13732; 33867</t>
+          <t>13746; 32190</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19790; 42388</t>
+          <t>19034; 41833</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10208; 27681</t>
+          <t>10925; 28471</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6185; 20255</t>
+          <t>6305; 20280</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14039; 32844</t>
+          <t>13962; 31654</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18789; 39294</t>
+          <t>17619; 38403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16304; 38079</t>
+          <t>17332; 39055</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18506; 40725</t>
+          <t>17711; 39944</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31661; 58212</t>
+          <t>31126; 58565</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28716; 54537</t>
+          <t>27265; 52722</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37066; 64231</t>
+          <t>37867; 64866</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7604; 24312</t>
+          <t>7586; 23565</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4021; 17219</t>
+          <t>4007; 17227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9262; 26473</t>
+          <t>8932; 25618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8766; 24201</t>
+          <t>9507; 24252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9524; 27559</t>
+          <t>9430; 27104</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3069; 14306</t>
+          <t>3041; 15221</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19701; 41373</t>
+          <t>19472; 41004</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15802; 38889</t>
+          <t>16340; 37835</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13854; 33987</t>
+          <t>14737; 33337</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11255; 28916</t>
+          <t>11302; 28647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10464; 29606</t>
+          <t>10268; 28466</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14010; 32348</t>
+          <t>13786; 32805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13510; 33595</t>
+          <t>13552; 32288</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19997; 43960</t>
+          <t>20768; 45561</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20016; 43498</t>
+          <t>20497; 44778</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27344; 53140</t>
+          <t>29026; 52290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35749; 65187</t>
+          <t>36750; 66956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38164; 66955</t>
+          <t>38190; 66662</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49747; 80395</t>
+          <t>49811; 80461</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35840; 65963</t>
+          <t>34584; 63186</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61151; 96900</t>
+          <t>61511; 96961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69534; 106829</t>
+          <t>68707; 105070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>68765; 106697</t>
+          <t>66714; 105433</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59388; 95811</t>
+          <t>59852; 96283</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>126092; 178096</t>
+          <t>127168; 175380</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>114248; 163248</t>
+          <t>111290; 159439</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>128980; 177268</t>
+          <t>130042; 179356</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C09-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,85</t>
+          <t>1,8; 4,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,39</t>
+          <t>0,82; 3,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,2</t>
+          <t>1,91; 5,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,3</t>
+          <t>2,81; 6,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,29</t>
+          <t>0,97; 3,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,84</t>
+          <t>1,16; 3,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,02</t>
+          <t>2,56; 5,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,64</t>
+          <t>1,12; 2,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,91</t>
+          <t>1,82; 4,02</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,94</t>
+          <t>1,35; 3,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,4</t>
+          <t>0,81; 2,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,88</t>
+          <t>1,69; 3,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,78</t>
+          <t>2,26; 4,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,41</t>
+          <t>1,88; 4,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,61</t>
+          <t>2,11; 4,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,84</t>
+          <t>2,09; 3,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,05</t>
+          <t>1,55; 3,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,85</t>
+          <t>2,19; 3,9</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,33</t>
+          <t>1,33; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,75</t>
+          <t>0,64; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,65</t>
+          <t>1,64; 4,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,15</t>
+          <t>1,55; 4,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,12</t>
+          <t>1,42; 4,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,63</t>
+          <t>0,52; 2,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,63</t>
+          <t>1,72; 3,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,95</t>
+          <t>1,31; 3,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,95</t>
+          <t>1,28; 2,92</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,05</t>
+          <t>1,67; 4,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,68</t>
+          <t>1,32; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,25</t>
+          <t>1,86; 4,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,98</t>
+          <t>1,63; 3,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,06</t>
+          <t>2,32; 4,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,11</t>
+          <t>2,25; 4,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,45</t>
+          <t>1,91; 3,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,0</t>
+          <t>2,15; 3,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,04</t>
+          <t>2,4; 4,1</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,28</t>
+          <t>2,03; 3,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,23</t>
+          <t>1,3; 2,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,64</t>
+          <t>2,26; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,84</t>
+          <t>2,54; 3,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,43</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,36</t>
+          <t>2,13; 3,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,38</t>
+          <t>2,44; 3,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,7</t>
+          <t>1,88; 2,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,24</t>
+          <t>2,36; 3,27</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8457; 23191</t>
+          <t>8583; 22180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5148; 20060</t>
+          <t>4863; 19587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10046; 27293</t>
+          <t>10046; 26363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14692; 33877</t>
+          <t>15096; 34193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6082; 20642</t>
+          <t>6103; 20494</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6478; 20892</t>
+          <t>6296; 20160</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26330; 51025</t>
+          <t>26056; 51318</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13746; 32190</t>
+          <t>13673; 33559</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19034; 41833</t>
+          <t>19442; 43012</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10925; 28471</t>
+          <t>9739; 27175</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6305; 20280</t>
+          <t>6844; 21072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13962; 31654</t>
+          <t>13787; 31882</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17619; 38403</t>
+          <t>18172; 38349</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17332; 39055</t>
+          <t>16680; 38760</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17711; 39944</t>
+          <t>18301; 41294</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31126; 58565</t>
+          <t>31835; 59192</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27265; 52722</t>
+          <t>26854; 53273</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37867; 64866</t>
+          <t>36828; 65639</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7586; 23565</t>
+          <t>7230; 24604</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4007; 17227</t>
+          <t>3991; 16462</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8932; 25618</t>
+          <t>9017; 25322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9507; 24252</t>
+          <t>9066; 24283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9430; 27104</t>
+          <t>9341; 26561</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3041; 15221</t>
+          <t>2988; 14406</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19472; 41004</t>
+          <t>19453; 41667</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16340; 37835</t>
+          <t>16884; 38774</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14737; 33337</t>
+          <t>14515; 32989</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11302; 28647</t>
+          <t>11775; 28645</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10268; 28466</t>
+          <t>10190; 29021</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13786; 32805</t>
+          <t>14357; 33064</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13552; 32288</t>
+          <t>13185; 32007</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20768; 45561</t>
+          <t>20854; 44108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20497; 44778</t>
+          <t>19689; 43254</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29026; 52290</t>
+          <t>28936; 54292</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36750; 66956</t>
+          <t>35947; 65181</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38190; 66662</t>
+          <t>39610; 67707</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49811; 80461</t>
+          <t>49727; 81908</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34584; 63186</t>
+          <t>36997; 66974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61511; 96961</t>
+          <t>60098; 94125</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68707; 105070</t>
+          <t>69568; 105202</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66714; 105433</t>
+          <t>69078; 106971</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>59852; 96283</t>
+          <t>61045; 97964</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>127168; 175380</t>
+          <t>126470; 175335</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111290; 159439</t>
+          <t>111187; 160618</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130042; 179356</t>
+          <t>130383; 180676</t>
         </is>
       </c>
     </row>
